--- a/dataset/construct/dataset_splits/data_size/50_percent/tum/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/50_percent/tum/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2868</v>
+        <v>2008</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,79 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.58796220244891</v>
+        <v>86.27327024235051</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>26.4462809917355</v>
       </c>
       <c r="E2" t="n">
-        <v>23.4375</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>52</v>
+        <v>245.9</v>
       </c>
       <c r="I2" t="n">
-        <v>12100</v>
+        <v>53.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>59.7</v>
       </c>
       <c r="K2" t="n">
-        <v>718</v>
+        <v>359.5</v>
       </c>
       <c r="L2" t="n">
-        <v>370</v>
+        <v>46.7</v>
       </c>
       <c r="M2" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1444</v>
+        <v>16.1</v>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>62.8</v>
       </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>6.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X2" t="n">
-        <v>22.3</v>
+        <v>23.3621512301397</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.244094488188976</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>23.3638910109498</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.8359153550381</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -727,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -739,22 +724,13 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>109</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>632</v>
+        <v>308</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,85 +738,85 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.13777473572139</v>
+        <v>87.22088089715309</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>20.5761316872427</v>
       </c>
       <c r="E3" t="n">
-        <v>28.0890109547142</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>666</v>
       </c>
       <c r="I3" t="n">
-        <v>176</v>
+        <v>391</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="K3" t="n">
-        <v>379</v>
+        <v>1279</v>
       </c>
       <c r="L3" t="n">
-        <v>491.8</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>284.9</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>1155.7</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
-        <v>140.4</v>
+        <v>137</v>
       </c>
       <c r="P3" t="n">
-        <v>193.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>377.5</v>
+        <v>18</v>
       </c>
       <c r="S3" t="n">
-        <v>12.6</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>17.6</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>30.2</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X3" t="n">
-        <v>26.55</v>
+        <v>22.0792760606539</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.187713310580205</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.5151515151515</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.2096759585991</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -855,30 +831,19 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>238</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>693</v>
+        <v>364</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,79 +851,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.651817628717</v>
+        <v>83.7306500177453</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27.639801313892</v>
       </c>
       <c r="E4" t="n">
-        <v>19.6623076682999</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="I4" t="n">
-        <v>1330</v>
+        <v>72</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>289</v>
       </c>
       <c r="L4" t="n">
-        <v>417</v>
+        <v>116</v>
       </c>
       <c r="M4" t="n">
-        <v>447</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>1573</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>193</v>
+        <v>21.15</v>
       </c>
       <c r="V4" t="n">
-        <v>242</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X4" t="n">
-        <v>25.1</v>
+        <v>20.8029488434442</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.304054054054054</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.7830404889228</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.8203626912254</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -976,31 +941,22 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1019</v>
+        <v>1094</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,79 +964,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84.97033370725281</v>
+        <v>74.44095254391971</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>25.3443526170798</v>
       </c>
       <c r="E5" t="n">
-        <v>30.1109905115367</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>420.7</v>
       </c>
       <c r="I5" t="n">
-        <v>340</v>
+        <v>199.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>296.8</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>916.7</v>
       </c>
       <c r="L5" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>561</v>
+        <v>32.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>98</v>
+        <v>35.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>96</v>
+        <v>23.25</v>
       </c>
       <c r="V5" t="n">
-        <v>96</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>23.3002291825821</v>
       </c>
       <c r="X5" t="n">
-        <v>24.3</v>
+        <v>22.8943655965997</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.232727272727273</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>24.1914947797301</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.6114412754479</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1101,30 +1057,21 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1429</v>
+        <v>300</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,86 +1079,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.07960906406061</v>
+        <v>87.77125827059091</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24.6913580246913</v>
       </c>
       <c r="E6" t="n">
-        <v>36.71875</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>539</v>
+      </c>
+      <c r="I6" t="n">
+        <v>316</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="K6" t="n">
-        <v>522.4</v>
+        <v>1001</v>
       </c>
       <c r="L6" t="n">
-        <v>255.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>169.8</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>89.5</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>117.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>25.55</v>
       </c>
       <c r="V6" t="n">
-        <v>8.800000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>25.8467023172906</v>
       </c>
       <c r="X6" t="n">
-        <v>23.45</v>
+        <v>25.4282983710565</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.138888888888889</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.7458619811561</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.6114412754479</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1220,33 +1169,24 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,41 +1194,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>85.260315042969</v>
+        <v>87.6778480619566</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>23.9389897746315</v>
       </c>
       <c r="E7" t="n">
-        <v>28.6501377410468</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>125</v>
+      </c>
+      <c r="I7" t="n">
+        <v>231</v>
+      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>591</v>
       </c>
       <c r="L7" t="n">
-        <v>294</v>
+        <v>15</v>
       </c>
       <c r="M7" t="n">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>619</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1297,34 +1239,34 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>27.85</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>28.7114845938375</v>
       </c>
       <c r="X7" t="n">
-        <v>23.05</v>
+        <v>27.1143398301643</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.206225680933852</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.176170013362</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1333,40 +1275,29 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1374,41 +1305,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82.2897330595483</v>
+        <v>78.96926572362921</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>27.7551020408163</v>
       </c>
       <c r="E8" t="n">
-        <v>31.25</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="I8" t="n">
+        <v>154</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="K8" t="n">
-        <v>192</v>
+        <v>400</v>
       </c>
       <c r="L8" t="n">
-        <v>39.8</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>32.1</v>
+        <v>21</v>
       </c>
       <c r="N8" t="n">
-        <v>263.9</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1417,34 +1350,34 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X8" t="n">
-        <v>22.65</v>
+        <v>21.4357677787856</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.173387096774194</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.5362872421696</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.0244421422418</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1459,36 +1392,27 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>551</v>
+        <v>2012</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1496,88 +1420,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>86.878606738155</v>
+        <v>84.8005503270211</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.5102040816326</v>
       </c>
       <c r="E9" t="n">
-        <v>23.1481481481481</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>564.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1010</v>
+        <v>316.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>120.3</v>
       </c>
       <c r="K9" t="n">
-        <v>852</v>
+        <v>1001.9</v>
       </c>
       <c r="L9" t="n">
-        <v>377</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>892</v>
+        <v>6.6</v>
       </c>
       <c r="N9" t="n">
-        <v>2121</v>
+        <v>15.3</v>
       </c>
       <c r="O9" t="n">
-        <v>300</v>
+        <v>116.3</v>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>204</v>
+        <v>24.85</v>
       </c>
       <c r="V9" t="n">
-        <v>474</v>
+        <v>0.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X9" t="n">
-        <v>23.7</v>
+        <v>24.8126692377086</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.197718631178707</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>23.5033791921504</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1586,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -1595,24 +1519,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>234</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1620,79 +1535,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82.85644725834661</v>
+        <v>88.2965738839455</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>32.8731097961867</v>
       </c>
       <c r="E10" t="n">
-        <v>24.6530314097881</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I10" t="n">
-        <v>4570</v>
+        <v>82</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="K10" t="n">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="L10" t="n">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>321</v>
+        <v>15</v>
       </c>
       <c r="N10" t="n">
-        <v>747</v>
+        <v>58</v>
       </c>
       <c r="O10" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="P10" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>106</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
-        <v>148</v>
+        <v>0.32</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>20.690094219506</v>
       </c>
       <c r="X10" t="n">
-        <v>21.9</v>
+        <v>19.8639809247436</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.308880308880309</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.8678380443086</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6802165106906</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1707,36 +1622,27 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2488</v>
+        <v>801</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,123 +1650,114 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86.902992211068</v>
+        <v>77.94204359647119</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>35.546875</v>
       </c>
       <c r="E11" t="n">
-        <v>23.191094619666</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>55</v>
+        <v>838</v>
       </c>
       <c r="I11" t="n">
-        <v>3410</v>
+        <v>779</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="K11" t="n">
-        <v>55.2</v>
+        <v>2291</v>
       </c>
       <c r="L11" t="n">
-        <v>37.3</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>28.1</v>
+        <v>265</v>
       </c>
       <c r="N11" t="n">
-        <v>120.6</v>
+        <v>146</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X11" t="n">
-        <v>22.2</v>
+        <v>22.5921534344381</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17283950617284</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.0588235294118</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.7540506465255</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>731</v>
+        <v>2046</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1868,86 +1765,88 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>81.0275846705706</v>
+        <v>82.70324825081759</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>22.6473769605191</v>
       </c>
       <c r="E12" t="n">
-        <v>17.9163307354653</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>319</v>
+      </c>
+      <c r="I12" t="n">
+        <v>367.5</v>
+      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>198.9</v>
       </c>
       <c r="K12" t="n">
-        <v>344</v>
+        <v>885.4</v>
       </c>
       <c r="L12" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>261.4</v>
+        <v>54.3</v>
       </c>
       <c r="N12" t="n">
-        <v>871.4</v>
+        <v>24.5</v>
       </c>
       <c r="O12" t="n">
-        <v>5.7</v>
+        <v>78.8</v>
       </c>
       <c r="P12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>50.2</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>24.1596638655462</v>
       </c>
       <c r="X12" t="n">
-        <v>23.15</v>
+        <v>23.4573020624089</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.291512915129151</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.2683982683983</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.7325659324369</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1962,27 +1861,18 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>288</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>700</v>
+        <v>615</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1990,82 +1880,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86.8191345349456</v>
+        <v>73.3180274799098</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>28.0379234593594</v>
       </c>
       <c r="E13" t="n">
-        <v>25.6055363321799</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="n">
-        <v>965</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>420</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>285</v>
-      </c>
-      <c r="M13" t="n">
-        <v>308</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1013</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>23.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X13" t="n">
-        <v>23.8</v>
+        <v>23.4491614055397</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.196969696969697</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>23.4220054480732</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2077,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2089,24 +1967,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2178</v>
+        <v>2847</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2114,83 +1983,85 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79.7736672624027</v>
+        <v>83.10646231018831</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>29.8649584487534</v>
       </c>
       <c r="E14" t="n">
-        <v>30.0432622977087</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="I14" t="n">
+        <v>197</v>
+      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K14" t="n">
-        <v>545.4</v>
+        <v>588</v>
       </c>
       <c r="L14" t="n">
-        <v>113.2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>43.6</v>
+        <v>51</v>
       </c>
       <c r="N14" t="n">
-        <v>702.2</v>
+        <v>241</v>
       </c>
       <c r="O14" t="n">
-        <v>62.3</v>
+        <v>292</v>
       </c>
       <c r="P14" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>69.59999999999999</v>
+        <v>193</v>
       </c>
       <c r="S14" t="n">
-        <v>16.8</v>
+        <v>201</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V14" t="n">
-        <v>16.8</v>
+        <v>0.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>20.7855869620576</v>
       </c>
       <c r="X14" t="n">
-        <v>25.1</v>
+        <v>20.1786711448505</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.181159420289855</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.3374076903489</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.9966585942398</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2202,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2211,22 +2082,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2234,121 +2098,112 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88.2965738839455</v>
+        <v>78.9525439196897</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>25.2493372048983</v>
       </c>
       <c r="E15" t="n">
-        <v>32.8731097961867</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>650</v>
+      </c>
+      <c r="I15" t="n">
+        <v>852</v>
+      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>646</v>
       </c>
       <c r="K15" t="n">
-        <v>52</v>
+        <v>2148</v>
       </c>
       <c r="L15" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M15" t="n">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="N15" t="n">
+        <v>148</v>
+      </c>
+      <c r="O15" t="n">
         <v>314</v>
       </c>
-      <c r="O15" t="n">
-        <v>15</v>
-      </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>27.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>27.7565571683219</v>
       </c>
       <c r="X15" t="n">
-        <v>20.6</v>
+        <v>27.0297101600648</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.318367346938776</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.690094219506</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.8639809247436</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>156</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>588</v>
+        <v>1662</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2356,86 +2211,88 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>86.977426040003</v>
+        <v>83.6203661875428</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>24.0054869684499</v>
       </c>
       <c r="E16" t="n">
-        <v>30.7173999207292</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="I16" t="n">
+        <v>52</v>
+      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>464</v>
       </c>
       <c r="K16" t="n">
-        <v>556</v>
+        <v>627</v>
       </c>
       <c r="L16" t="n">
-        <v>582</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1456</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>23.95</v>
       </c>
       <c r="V16" t="n">
-        <v>40</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X16" t="n">
-        <v>26.65</v>
+        <v>23.3130652972889</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.180887372013652</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>27.2472625413802</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>26.8406888888731</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2453,24 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>122</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>582</v>
+        <v>481</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2478,85 +2324,85 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84.6962753821583</v>
+        <v>88.08028322812891</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>23.5078053259871</v>
       </c>
       <c r="E17" t="n">
-        <v>24.5351239669421</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>45</v>
+        <v>726</v>
       </c>
       <c r="I17" t="n">
-        <v>3590</v>
+        <v>396</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="K17" t="n">
-        <v>739</v>
+        <v>1407</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>104</v>
       </c>
       <c r="M17" t="n">
-        <v>485</v>
+        <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>1794</v>
+        <v>38</v>
       </c>
       <c r="O17" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="P17" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X17" t="n">
-        <v>29.85</v>
+        <v>21.6131702613684</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.313559322033898</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>29.921059332824</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>28.8077434310377</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2577,24 +2423,15 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>308</v>
+        <v>683</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2602,121 +2439,114 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87.22088089715309</v>
+        <v>77.1018803711309</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>24.5674740484429</v>
       </c>
       <c r="E18" t="n">
-        <v>20.5761316872427</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>553</v>
       </c>
       <c r="I18" t="n">
-        <v>3340</v>
+        <v>462</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>537</v>
       </c>
       <c r="K18" t="n">
-        <v>666</v>
+        <v>1552</v>
       </c>
       <c r="L18" t="n">
-        <v>391</v>
+        <v>26</v>
       </c>
       <c r="M18" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1279</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="P18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>25.3</v>
       </c>
       <c r="V18" t="n">
-        <v>31</v>
+        <v>0.26</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>23.8794571386939</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.218623481781376</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.0792760606539</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN18" t="inlineStr"/>
+        <v>176</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2724,85 +2554,85 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>85.36462278500269</v>
+        <v>72.13777473572139</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>28.0890109547142</v>
       </c>
       <c r="E19" t="n">
-        <v>30.4271978579252</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>45</v>
+        <v>379</v>
       </c>
       <c r="I19" t="n">
-        <v>2040</v>
+        <v>491.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>284.9</v>
       </c>
       <c r="K19" t="n">
-        <v>78</v>
+        <v>1155.7</v>
       </c>
       <c r="L19" t="n">
-        <v>26.4</v>
+        <v>140.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>193.1</v>
       </c>
       <c r="N19" t="n">
-        <v>104.4</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>377.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>26.5151515151515</v>
       </c>
       <c r="X19" t="n">
-        <v>22.9</v>
+        <v>26.2096759585991</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.271698113207547</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6736985933985</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2811,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -2823,24 +2653,15 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>321</v>
+        <v>2073</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2848,80 +2669,82 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79.8068831596826</v>
+        <v>86.328758302279</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>33.6326530612244</v>
       </c>
       <c r="E20" t="n">
-        <v>24.1684694429421</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>1095.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>600</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>673.8</v>
       </c>
       <c r="K20" t="n">
-        <v>281</v>
+        <v>2369.1</v>
       </c>
       <c r="L20" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>166</v>
+        <v>31.4</v>
       </c>
       <c r="N20" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>19</v>
+        <v>31.4</v>
       </c>
       <c r="P20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>30.35</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>29.9847211611918</v>
       </c>
       <c r="X20" t="n">
-        <v>23.7</v>
+        <v>29.7211204525439</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.237918215613383</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>23.6652872775905</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2930,39 +2753,30 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>152</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>514</v>
+        <v>347</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2970,123 +2784,110 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>86.1886265115218</v>
+        <v>84.5302151304282</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>27.0416441319632</v>
       </c>
       <c r="E21" t="n">
-        <v>26.813590449954</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>346</v>
       </c>
       <c r="I21" t="n">
-        <v>1190</v>
+        <v>162.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>134.3</v>
       </c>
       <c r="K21" t="n">
-        <v>560</v>
+        <v>643.1</v>
       </c>
       <c r="L21" t="n">
-        <v>108</v>
+        <v>39.2</v>
       </c>
       <c r="M21" t="n">
-        <v>277</v>
+        <v>8.6</v>
       </c>
       <c r="N21" t="n">
-        <v>945</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>48.8</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>38.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>46.8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X21" t="n">
-        <v>21.9</v>
+        <v>26.0831054612881</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.295719844357977</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.2816399286988</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.903660546599</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>186</v>
-      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>300</v>
+        <v>2419</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3094,86 +2895,88 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>87.77125827059091</v>
+        <v>83.00703576951349</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>24.1588179685585</v>
       </c>
       <c r="E22" t="n">
-        <v>24.6913580246913</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>52</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>441.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>341.5</v>
+      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>36.7</v>
       </c>
       <c r="K22" t="n">
-        <v>539</v>
+        <v>819.5</v>
       </c>
       <c r="L22" t="n">
-        <v>316</v>
+        <v>36.3</v>
       </c>
       <c r="M22" t="n">
-        <v>146</v>
+        <v>17.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1001</v>
+        <v>9.9</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>22.95</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>23.4275528393175</v>
       </c>
       <c r="X22" t="n">
-        <v>25.55</v>
+        <v>23.0743446333452</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.128205128205128</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>25.8467023172906</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>25.4282983710565</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3182,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3191,24 +2994,15 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>190</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>619</v>
+        <v>899</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3216,82 +3010,82 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74.8920669505919</v>
+        <v>80.2974793076787</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>27.7769298861451</v>
       </c>
       <c r="E23" t="n">
-        <v>24.8015873015873</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>407</v>
       </c>
       <c r="I23" t="n">
-        <v>498</v>
+        <v>208</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="K23" t="n">
-        <v>374</v>
+        <v>919</v>
       </c>
       <c r="L23" t="n">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="M23" t="n">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="N23" t="n">
-        <v>739</v>
+        <v>155</v>
       </c>
       <c r="O23" t="n">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>8</v>
       </c>
-      <c r="R23" t="n">
-        <v>82</v>
-      </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X23" t="n">
-        <v>24.4</v>
+        <v>26.9117274486368</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.199261992619926</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>25.0509294626942</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>24.6608768976369</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3300,39 +3094,30 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1496</v>
+        <v>881</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3340,86 +3125,88 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>87.1905014006135</v>
+        <v>80.0008762390042</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>42.2218052167386</v>
       </c>
       <c r="E24" t="n">
-        <v>26.0275824770146</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>72</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K24" t="n">
-        <v>756.1</v>
+        <v>290</v>
       </c>
       <c r="L24" t="n">
-        <v>424.9</v>
+        <v>62</v>
       </c>
       <c r="M24" t="n">
-        <v>401.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1582.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>242.5</v>
+        <v>62</v>
       </c>
       <c r="P24" t="n">
-        <v>77.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>80.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>400.1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>182.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>10.3</v>
+        <v>24.45</v>
       </c>
       <c r="V24" t="n">
-        <v>194.2</v>
+        <v>0.23</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>25.1782531194296</v>
       </c>
       <c r="X24" t="n">
-        <v>28.2</v>
+        <v>24.3805715703063</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2375</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>28.2658517952636</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>27.8049959638069</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3437,24 +3224,15 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>496</v>
+        <v>1572</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3462,88 +3240,88 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.640161672624</v>
+        <v>86.5638272872462</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>24.8015873015873</v>
       </c>
       <c r="E25" t="n">
-        <v>29.7265160523186</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>37</v>
+        <v>117.8</v>
       </c>
       <c r="I25" t="n">
-        <v>8130</v>
+        <v>166</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>264.6</v>
       </c>
       <c r="K25" t="n">
-        <v>696</v>
+        <v>548.4000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>233</v>
+        <v>7.3</v>
       </c>
       <c r="M25" t="n">
-        <v>339</v>
+        <v>40.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1268</v>
+        <v>18.4</v>
       </c>
       <c r="O25" t="n">
-        <v>131</v>
+        <v>66.19999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>133</v>
+        <v>19.1</v>
       </c>
       <c r="S25" t="n">
-        <v>75</v>
+        <v>19.1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>45</v>
+        <v>24.4</v>
       </c>
       <c r="V25" t="n">
-        <v>120</v>
+        <v>0.17</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X25" t="n">
-        <v>27.2</v>
+        <v>24.1181250506758</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.198675496688742</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>26.7379679144385</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>26.4345313179585</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3561,22 +3339,15 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>936</v>
+        <v>1205</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3584,94 +3355,94 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>91.0289564795802</v>
+        <v>77.3262297196238</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E26" t="n">
-        <v>23.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="I26" t="n">
-        <v>10700</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="L26" t="n">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>40</v>
+        <v>20.8</v>
       </c>
       <c r="V26" t="n">
-        <v>40</v>
+        <v>0.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X26" t="n">
-        <v>20.05</v>
+        <v>20.8945249963572</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.209821428571429</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.3717850776674</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.8319163664306</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -3683,24 +3454,15 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1315</v>
+        <v>2413</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3708,85 +3470,85 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>77.34847025756081</v>
+        <v>83.4834113494055</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>37.6542220797949</v>
       </c>
       <c r="E27" t="n">
-        <v>29.0687732977668</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>1003.9</v>
       </c>
       <c r="I27" t="n">
-        <v>933</v>
+        <v>83</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="K27" t="n">
-        <v>645.9</v>
+        <v>1109.1</v>
       </c>
       <c r="L27" t="n">
-        <v>346.9</v>
+        <v>34.4</v>
       </c>
       <c r="M27" t="n">
-        <v>419.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1412.3</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="P27" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V27" t="n">
-        <v>26</v>
+        <v>0.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>23.1729055258467</v>
       </c>
       <c r="X27" t="n">
-        <v>26.8</v>
+        <v>22.6034185328367</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.207357859531773</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>27.6292335115865</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>26.9920118011893</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -3801,25 +3563,16 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
